--- a/IV_4.5K_T1.xlsx
+++ b/IV_4.5K_T1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1939,10 +1939,10 @@
         <v>5.5837900000000003E-5</v>
       </c>
       <c r="AA16">
-        <v>18.75</v>
+        <v>17.1875</v>
       </c>
       <c r="AB16">
-        <v>2.4660000000000001E-2</v>
+        <v>1.116E-2</v>
       </c>
       <c r="AC16">
         <v>17.1875</v>
@@ -2055,10 +2055,10 @@
         <v>1.6751400000000001E-4</v>
       </c>
       <c r="AA17">
-        <v>20.3125</v>
+        <v>18.75</v>
       </c>
       <c r="AB17">
-        <v>2.6700000000000002E-2</v>
+        <v>2.4660000000000001E-2</v>
       </c>
       <c r="AC17">
         <v>18.75</v>
@@ -2171,10 +2171,10 @@
         <v>8.0406599999999998E-4</v>
       </c>
       <c r="AA18">
-        <v>21.875</v>
+        <v>20.3125</v>
       </c>
       <c r="AB18">
-        <v>2.877E-2</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="AC18">
         <v>20.3125</v>
@@ -2287,10 +2287,10 @@
         <v>4.45618E-4</v>
       </c>
       <c r="AA19">
-        <v>23.4375</v>
+        <v>21.875</v>
       </c>
       <c r="AB19">
-        <v>3.0810000000000001E-2</v>
+        <v>2.877E-2</v>
       </c>
       <c r="AC19">
         <v>21.875</v>
@@ -2403,10 +2403,10 @@
         <v>2.5479999999999999E-2</v>
       </c>
       <c r="AA20">
-        <v>25</v>
+        <v>23.4375</v>
       </c>
       <c r="AB20">
-        <v>3.286E-2</v>
+        <v>3.0810000000000001E-2</v>
       </c>
       <c r="AC20">
         <v>23.4375</v>
@@ -2519,10 +2519,10 @@
         <v>3.2930000000000001E-2</v>
       </c>
       <c r="AA21">
-        <v>26.5625</v>
+        <v>25</v>
       </c>
       <c r="AB21">
-        <v>3.49E-2</v>
+        <v>3.286E-2</v>
       </c>
       <c r="AC21">
         <v>25</v>
@@ -2635,10 +2635,10 @@
         <v>3.499E-2</v>
       </c>
       <c r="AA22">
-        <v>28.125</v>
+        <v>26.5625</v>
       </c>
       <c r="AB22">
-        <v>3.6949999999999997E-2</v>
+        <v>3.49E-2</v>
       </c>
       <c r="AC22">
         <v>26.5625</v>
@@ -2751,10 +2751,10 @@
         <v>3.705E-2</v>
       </c>
       <c r="AA23">
-        <v>29.6875</v>
+        <v>28.125</v>
       </c>
       <c r="AB23">
-        <v>3.9E-2</v>
+        <v>3.6949999999999997E-2</v>
       </c>
       <c r="AC23">
         <v>28.125</v>
@@ -2867,10 +2867,10 @@
         <v>3.9100000000000003E-2</v>
       </c>
       <c r="AA24">
-        <v>31.25</v>
+        <v>29.6875</v>
       </c>
       <c r="AB24">
-        <v>4.104E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="AC24">
         <v>29.6875</v>
@@ -2983,10 +2983,10 @@
         <v>4.1149999999999999E-2</v>
       </c>
       <c r="AA25">
-        <v>32.8125</v>
+        <v>31.25</v>
       </c>
       <c r="AB25">
-        <v>4.308E-2</v>
+        <v>4.104E-2</v>
       </c>
       <c r="AC25">
         <v>31.25</v>
@@ -3099,10 +3099,10 @@
         <v>4.3209999999999998E-2</v>
       </c>
       <c r="AA26">
-        <v>34.375</v>
+        <v>32.8125</v>
       </c>
       <c r="AB26">
-        <v>4.514E-2</v>
+        <v>4.308E-2</v>
       </c>
       <c r="AC26">
         <v>32.8125</v>
@@ -3215,10 +3215,10 @@
         <v>4.5260000000000002E-2</v>
       </c>
       <c r="AA27">
-        <v>35.9375</v>
+        <v>34.375</v>
       </c>
       <c r="AB27">
-        <v>4.718E-2</v>
+        <v>4.514E-2</v>
       </c>
       <c r="AC27">
         <v>34.375</v>
@@ -3331,10 +3331,10 @@
         <v>4.7309999999999998E-2</v>
       </c>
       <c r="AA28">
-        <v>37.5</v>
+        <v>35.9375</v>
       </c>
       <c r="AB28">
-        <v>4.9250000000000002E-2</v>
+        <v>4.718E-2</v>
       </c>
       <c r="AC28">
         <v>35.9375</v>
@@ -3447,10 +3447,10 @@
         <v>4.9369999999999997E-2</v>
       </c>
       <c r="AA29">
-        <v>39.0625</v>
+        <v>37.5</v>
       </c>
       <c r="AB29">
-        <v>5.1290000000000002E-2</v>
+        <v>4.9250000000000002E-2</v>
       </c>
       <c r="AC29">
         <v>37.5</v>
@@ -3563,10 +3563,10 @@
         <v>5.1429999999999997E-2</v>
       </c>
       <c r="AA30">
-        <v>40.625</v>
+        <v>39.0625</v>
       </c>
       <c r="AB30">
-        <v>5.3350000000000002E-2</v>
+        <v>5.1290000000000002E-2</v>
       </c>
       <c r="AC30">
         <v>39.0625</v>
@@ -3679,10 +3679,10 @@
         <v>5.3490000000000003E-2</v>
       </c>
       <c r="AA31">
-        <v>42.1875</v>
+        <v>40.625</v>
       </c>
       <c r="AB31">
-        <v>5.5390000000000002E-2</v>
+        <v>5.3350000000000002E-2</v>
       </c>
       <c r="AC31">
         <v>40.625</v>
@@ -3795,10 +3795,10 @@
         <v>5.5550000000000002E-2</v>
       </c>
       <c r="AA32">
-        <v>43.75</v>
+        <v>42.1875</v>
       </c>
       <c r="AB32">
-        <v>5.7430000000000002E-2</v>
+        <v>5.5390000000000002E-2</v>
       </c>
       <c r="AC32">
         <v>42.1875</v>
@@ -3911,10 +3911,10 @@
         <v>5.7590000000000002E-2</v>
       </c>
       <c r="AA33">
-        <v>45.3125</v>
+        <v>43.75</v>
       </c>
       <c r="AB33">
-        <v>5.9479999999999998E-2</v>
+        <v>5.7430000000000002E-2</v>
       </c>
       <c r="AC33">
         <v>43.75</v>
@@ -4027,10 +4027,10 @@
         <v>5.9650000000000002E-2</v>
       </c>
       <c r="AA34">
-        <v>46.875</v>
+        <v>45.3125</v>
       </c>
       <c r="AB34">
-        <v>6.1530000000000001E-2</v>
+        <v>5.9479999999999998E-2</v>
       </c>
       <c r="AC34">
         <v>45.3125</v>
@@ -4143,10 +4143,10 @@
         <v>6.1699999999999998E-2</v>
       </c>
       <c r="AA35">
-        <v>48.4375</v>
+        <v>46.875</v>
       </c>
       <c r="AB35">
-        <v>6.3589999999999994E-2</v>
+        <v>6.1530000000000001E-2</v>
       </c>
       <c r="AC35">
         <v>46.875</v>
@@ -4259,10 +4259,10 @@
         <v>6.3759999999999997E-2</v>
       </c>
       <c r="AA36">
-        <v>50</v>
+        <v>48.4375</v>
       </c>
       <c r="AB36">
-        <v>6.5699999999999995E-2</v>
+        <v>6.3589999999999994E-2</v>
       </c>
       <c r="AC36">
         <v>48.4375</v>
@@ -4375,10 +4375,10 @@
         <v>6.5879999999999994E-2</v>
       </c>
       <c r="AA37">
-        <v>51.5625</v>
+        <v>50</v>
       </c>
       <c r="AB37">
-        <v>6.7750000000000005E-2</v>
+        <v>6.5699999999999995E-2</v>
       </c>
       <c r="AC37">
         <v>50</v>
@@ -4491,10 +4491,10 @@
         <v>6.7930000000000004E-2</v>
       </c>
       <c r="AA38">
-        <v>53.125</v>
+        <v>51.5625</v>
       </c>
       <c r="AB38">
-        <v>6.9809999999999997E-2</v>
+        <v>6.7750000000000005E-2</v>
       </c>
       <c r="AC38">
         <v>51.5625</v>
@@ -4607,10 +4607,10 @@
         <v>6.9989999999999997E-2</v>
       </c>
       <c r="AA39">
-        <v>54.6875</v>
+        <v>53.125</v>
       </c>
       <c r="AB39">
-        <v>7.1849999999999997E-2</v>
+        <v>6.9809999999999997E-2</v>
       </c>
       <c r="AC39">
         <v>53.125</v>
@@ -4723,10 +4723,10 @@
         <v>7.2040000000000007E-2</v>
       </c>
       <c r="AA40">
-        <v>56.25</v>
+        <v>54.6875</v>
       </c>
       <c r="AB40">
-        <v>7.3899999999999993E-2</v>
+        <v>7.1849999999999997E-2</v>
       </c>
       <c r="AC40">
         <v>54.6875</v>
@@ -4839,10 +4839,10 @@
         <v>7.4099999999999999E-2</v>
       </c>
       <c r="AA41">
-        <v>57.8125</v>
+        <v>56.25</v>
       </c>
       <c r="AB41">
-        <v>7.5950000000000004E-2</v>
+        <v>7.3899999999999993E-2</v>
       </c>
       <c r="AC41">
         <v>56.25</v>
@@ -4955,10 +4955,10 @@
         <v>7.6149999999999995E-2</v>
       </c>
       <c r="AA42">
-        <v>59.375</v>
+        <v>57.8125</v>
       </c>
       <c r="AB42">
-        <v>7.8009999999999996E-2</v>
+        <v>7.5950000000000004E-2</v>
       </c>
       <c r="AC42">
         <v>57.8125</v>
@@ -5071,10 +5071,10 @@
         <v>7.8219999999999998E-2</v>
       </c>
       <c r="AA43">
-        <v>60.9375</v>
+        <v>59.375</v>
       </c>
       <c r="AB43">
-        <v>8.0070000000000002E-2</v>
+        <v>7.8009999999999996E-2</v>
       </c>
       <c r="AC43">
         <v>59.375</v>
@@ -5190,7 +5190,7 @@
         <v>60.9375</v>
       </c>
       <c r="AB44">
-        <v>7.9869999999999997E-2</v>
+        <v>8.0070000000000002E-2</v>
       </c>
       <c r="AC44">
         <v>60.9375</v>
@@ -5303,10 +5303,10 @@
         <v>8.0070000000000002E-2</v>
       </c>
       <c r="AA45">
-        <v>59.375</v>
+        <v>60.9375</v>
       </c>
       <c r="AB45">
-        <v>7.7799999999999994E-2</v>
+        <v>7.9869999999999997E-2</v>
       </c>
       <c r="AC45">
         <v>60.9375</v>
@@ -5419,10 +5419,10 @@
         <v>7.8009999999999996E-2</v>
       </c>
       <c r="AA46">
-        <v>57.8125</v>
+        <v>59.375</v>
       </c>
       <c r="AB46">
-        <v>7.5759999999999994E-2</v>
+        <v>7.7799999999999994E-2</v>
       </c>
       <c r="AC46">
         <v>59.375</v>
@@ -5535,10 +5535,10 @@
         <v>7.5950000000000004E-2</v>
       </c>
       <c r="AA47">
-        <v>56.25</v>
+        <v>57.8125</v>
       </c>
       <c r="AB47">
-        <v>7.3709999999999998E-2</v>
+        <v>7.5759999999999994E-2</v>
       </c>
       <c r="AC47">
         <v>57.8125</v>
@@ -5651,10 +5651,10 @@
         <v>7.3899999999999993E-2</v>
       </c>
       <c r="AA48">
-        <v>54.6875</v>
+        <v>56.25</v>
       </c>
       <c r="AB48">
-        <v>7.1650000000000005E-2</v>
+        <v>7.3709999999999998E-2</v>
       </c>
       <c r="AC48">
         <v>56.25</v>
@@ -5767,10 +5767,10 @@
         <v>7.1830000000000005E-2</v>
       </c>
       <c r="AA49">
-        <v>53.125</v>
+        <v>54.6875</v>
       </c>
       <c r="AB49">
-        <v>6.9599999999999995E-2</v>
+        <v>7.1650000000000005E-2</v>
       </c>
       <c r="AC49">
         <v>54.6875</v>
@@ -5883,10 +5883,10 @@
         <v>6.9760000000000003E-2</v>
       </c>
       <c r="AA50">
-        <v>51.5625</v>
+        <v>53.125</v>
       </c>
       <c r="AB50">
-        <v>6.7540000000000003E-2</v>
+        <v>6.9599999999999995E-2</v>
       </c>
       <c r="AC50">
         <v>53.125</v>
@@ -5999,10 +5999,10 @@
         <v>6.7720000000000002E-2</v>
       </c>
       <c r="AA51">
-        <v>50</v>
+        <v>51.5625</v>
       </c>
       <c r="AB51">
-        <v>6.5420000000000006E-2</v>
+        <v>6.7540000000000003E-2</v>
       </c>
       <c r="AC51">
         <v>51.5625</v>
@@ -6115,10 +6115,10 @@
         <v>6.5600000000000006E-2</v>
       </c>
       <c r="AA52">
-        <v>48.4375</v>
+        <v>50</v>
       </c>
       <c r="AB52">
-        <v>6.336E-2</v>
+        <v>6.5420000000000006E-2</v>
       </c>
       <c r="AC52">
         <v>50</v>
@@ -6231,10 +6231,10 @@
         <v>6.3539999999999999E-2</v>
       </c>
       <c r="AA53">
-        <v>46.875</v>
+        <v>48.4375</v>
       </c>
       <c r="AB53">
-        <v>6.13E-2</v>
+        <v>6.336E-2</v>
       </c>
       <c r="AC53">
         <v>48.4375</v>
@@ -6347,10 +6347,10 @@
         <v>6.148E-2</v>
       </c>
       <c r="AA54">
-        <v>45.3125</v>
+        <v>46.875</v>
       </c>
       <c r="AB54">
-        <v>5.9240000000000001E-2</v>
+        <v>6.13E-2</v>
       </c>
       <c r="AC54">
         <v>46.875</v>
@@ -6463,10 +6463,10 @@
         <v>5.9420000000000001E-2</v>
       </c>
       <c r="AA55">
-        <v>43.75</v>
+        <v>45.3125</v>
       </c>
       <c r="AB55">
-        <v>5.7200000000000001E-2</v>
+        <v>5.9240000000000001E-2</v>
       </c>
       <c r="AC55">
         <v>45.3125</v>
@@ -6579,10 +6579,10 @@
         <v>5.7369999999999997E-2</v>
       </c>
       <c r="AA56">
-        <v>42.1875</v>
+        <v>43.75</v>
       </c>
       <c r="AB56">
-        <v>5.5160000000000001E-2</v>
+        <v>5.7200000000000001E-2</v>
       </c>
       <c r="AC56">
         <v>43.75</v>
@@ -6695,10 +6695,10 @@
         <v>5.5309999999999998E-2</v>
       </c>
       <c r="AA57">
-        <v>40.625</v>
+        <v>42.1875</v>
       </c>
       <c r="AB57">
-        <v>5.3089999999999998E-2</v>
+        <v>5.5160000000000001E-2</v>
       </c>
       <c r="AC57">
         <v>42.1875</v>
@@ -6811,10 +6811,10 @@
         <v>5.3249999999999999E-2</v>
       </c>
       <c r="AA58">
-        <v>39.0625</v>
+        <v>40.625</v>
       </c>
       <c r="AB58">
-        <v>5.1049999999999998E-2</v>
+        <v>5.3089999999999998E-2</v>
       </c>
       <c r="AC58">
         <v>40.625</v>
@@ -6927,10 +6927,10 @@
         <v>5.1189999999999999E-2</v>
       </c>
       <c r="AA59">
-        <v>37.5</v>
+        <v>39.0625</v>
       </c>
       <c r="AB59">
-        <v>4.8980000000000003E-2</v>
+        <v>5.1049999999999998E-2</v>
       </c>
       <c r="AC59">
         <v>39.0625</v>
@@ -7043,10 +7043,10 @@
         <v>4.913E-2</v>
       </c>
       <c r="AA60">
-        <v>35.9375</v>
+        <v>37.5</v>
       </c>
       <c r="AB60">
-        <v>4.6929999999999999E-2</v>
+        <v>4.8980000000000003E-2</v>
       </c>
       <c r="AC60">
         <v>37.5</v>
@@ -7159,10 +7159,10 @@
         <v>4.7070000000000001E-2</v>
       </c>
       <c r="AA61">
-        <v>34.375</v>
+        <v>35.9375</v>
       </c>
       <c r="AB61">
-        <v>4.487E-2</v>
+        <v>4.6929999999999999E-2</v>
       </c>
       <c r="AC61">
         <v>35.9375</v>
@@ -7275,10 +7275,10 @@
         <v>4.5019999999999998E-2</v>
       </c>
       <c r="AA62">
-        <v>32.8125</v>
+        <v>34.375</v>
       </c>
       <c r="AB62">
-        <v>4.2840000000000003E-2</v>
+        <v>4.487E-2</v>
       </c>
       <c r="AC62">
         <v>34.375</v>
@@ -7391,10 +7391,10 @@
         <v>4.2959999999999998E-2</v>
       </c>
       <c r="AA63">
-        <v>31.25</v>
+        <v>32.8125</v>
       </c>
       <c r="AB63">
-        <v>4.0800000000000003E-2</v>
+        <v>4.2840000000000003E-2</v>
       </c>
       <c r="AC63">
         <v>32.8125</v>
@@ -7507,10 +7507,10 @@
         <v>4.0910000000000002E-2</v>
       </c>
       <c r="AA64">
-        <v>29.6875</v>
+        <v>31.25</v>
       </c>
       <c r="AB64">
-        <v>3.8739999999999997E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="AC64">
         <v>31.25</v>
@@ -7623,10 +7623,10 @@
         <v>3.8859999999999999E-2</v>
       </c>
       <c r="AA65">
-        <v>28.125</v>
+        <v>29.6875</v>
       </c>
       <c r="AB65">
-        <v>3.669E-2</v>
+        <v>3.8739999999999997E-2</v>
       </c>
       <c r="AC65">
         <v>29.6875</v>
@@ -7739,10 +7739,10 @@
         <v>3.6799999999999999E-2</v>
       </c>
       <c r="AA66">
-        <v>26.5625</v>
+        <v>28.125</v>
       </c>
       <c r="AB66">
-        <v>3.4639999999999997E-2</v>
+        <v>3.669E-2</v>
       </c>
       <c r="AC66">
         <v>28.125</v>
@@ -7855,10 +7855,10 @@
         <v>3.474E-2</v>
       </c>
       <c r="AA67">
-        <v>25</v>
+        <v>26.5625</v>
       </c>
       <c r="AB67">
-        <v>3.2590000000000001E-2</v>
+        <v>3.4639999999999997E-2</v>
       </c>
       <c r="AC67">
         <v>26.5625</v>
@@ -7971,10 +7971,10 @@
         <v>3.2689999999999997E-2</v>
       </c>
       <c r="AA68">
-        <v>23.4375</v>
+        <v>25</v>
       </c>
       <c r="AB68">
-        <v>3.0540000000000001E-2</v>
+        <v>3.2590000000000001E-2</v>
       </c>
       <c r="AC68">
         <v>25</v>
@@ -8087,10 +8087,10 @@
         <v>3.0640000000000001E-2</v>
       </c>
       <c r="AA69">
-        <v>21.875</v>
+        <v>23.4375</v>
       </c>
       <c r="AB69">
-        <v>2.8490000000000001E-2</v>
+        <v>3.0540000000000001E-2</v>
       </c>
       <c r="AC69">
         <v>23.4375</v>
@@ -8203,10 +8203,10 @@
         <v>2.8580000000000001E-2</v>
       </c>
       <c r="AA70">
-        <v>20.3125</v>
+        <v>21.875</v>
       </c>
       <c r="AB70">
-        <v>2.6440000000000002E-2</v>
+        <v>2.8490000000000001E-2</v>
       </c>
       <c r="AC70">
         <v>21.875</v>
@@ -8319,10 +8319,10 @@
         <v>2.6519999999999998E-2</v>
       </c>
       <c r="AA71">
-        <v>18.75</v>
+        <v>20.3125</v>
       </c>
       <c r="AB71">
-        <v>2.4400000000000002E-2</v>
+        <v>2.6440000000000002E-2</v>
       </c>
       <c r="AC71">
         <v>20.3125</v>
@@ -8435,10 +8435,10 @@
         <v>2.4469999999999999E-2</v>
       </c>
       <c r="AA72">
-        <v>17.1875</v>
+        <v>18.75</v>
       </c>
       <c r="AB72">
-        <v>2.2349999999999998E-2</v>
+        <v>2.4400000000000002E-2</v>
       </c>
       <c r="AC72">
         <v>18.75</v>
@@ -8551,10 +8551,10 @@
         <v>2.2409999999999999E-2</v>
       </c>
       <c r="AA73">
-        <v>15.625</v>
+        <v>17.1875</v>
       </c>
       <c r="AB73">
-        <v>2.0289999999999999E-2</v>
+        <v>2.2349999999999998E-2</v>
       </c>
       <c r="AC73">
         <v>17.1875</v>
@@ -8667,10 +8667,10 @@
         <v>2.035E-2</v>
       </c>
       <c r="AA74">
-        <v>14.0625</v>
+        <v>15.625</v>
       </c>
       <c r="AB74">
-        <v>1.8239999999999999E-2</v>
+        <v>2.0289999999999999E-2</v>
       </c>
       <c r="AC74">
         <v>15.625</v>
@@ -8783,10 +8783,10 @@
         <v>1.823E-2</v>
       </c>
       <c r="AA75">
-        <v>12.5</v>
+        <v>14.0625</v>
       </c>
       <c r="AB75">
-        <v>1.61E-2</v>
+        <v>1.8239999999999999E-2</v>
       </c>
       <c r="AC75">
         <v>14.0625</v>
@@ -8899,10 +8899,10 @@
         <v>1.525E-2</v>
       </c>
       <c r="AA76">
-        <v>10.9375</v>
+        <v>12.5</v>
       </c>
       <c r="AB76">
-        <v>1.332E-2</v>
+        <v>1.61E-2</v>
       </c>
       <c r="AC76">
         <v>12.5</v>
@@ -9015,10 +9015,10 @@
         <v>4.8500000000000001E-3</v>
       </c>
       <c r="AA77">
-        <v>9.375</v>
+        <v>10.9375</v>
       </c>
       <c r="AB77">
-        <v>6.9499999999999996E-3</v>
+        <v>1.332E-2</v>
       </c>
       <c r="AC77">
         <v>10.9375</v>
@@ -9131,10 +9131,10 @@
         <v>3.4619499999999999E-4</v>
       </c>
       <c r="AA78">
-        <v>7.8125</v>
+        <v>9.375</v>
       </c>
       <c r="AB78">
-        <v>1.6000000000000001E-3</v>
+        <v>6.9499999999999996E-3</v>
       </c>
       <c r="AC78">
         <v>9.375</v>
@@ -9247,10 +9247,10 @@
         <v>7.8173100000000005E-5</v>
       </c>
       <c r="AA79">
-        <v>6.25</v>
+        <v>7.8125</v>
       </c>
       <c r="AB79" s="1">
-        <v>4.5787099999999999E-4</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="AC79">
         <v>7.8125</v>
@@ -9363,10 +9363,10 @@
         <v>1.11676E-5</v>
       </c>
       <c r="AA80">
-        <v>4.6875</v>
+        <v>6.25</v>
       </c>
       <c r="AB80" s="1">
-        <v>1.3401099999999999E-4</v>
+        <v>4.5787099999999999E-4</v>
       </c>
       <c r="AC80">
         <v>6.25</v>
@@ -9479,10 +9479,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>3.125</v>
+        <v>4.6875</v>
       </c>
       <c r="AB81" s="1">
-        <v>2.2335199999999999E-5</v>
+        <v>1.3401099999999999E-4</v>
       </c>
       <c r="AC81">
         <v>4.6875</v>
@@ -9595,10 +9595,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>1.5625</v>
-      </c>
-      <c r="AB82">
-        <v>0</v>
+        <v>3.125</v>
+      </c>
+      <c r="AB82" s="1">
+        <v>2.2335199999999999E-5</v>
       </c>
       <c r="AC82">
         <v>3.125</v>
@@ -9711,7 +9711,7 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.5625</v>
       </c>
       <c r="AB83">
         <v>0</v>
@@ -9827,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>-1.5625</v>
+        <v>0</v>
       </c>
       <c r="AB84">
         <v>0</v>
@@ -9943,10 +9943,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>-3.125</v>
+        <v>-1.5625</v>
       </c>
       <c r="AB85" s="1">
-        <v>-1.11676E-5</v>
+        <v>0</v>
       </c>
       <c r="AC85">
         <v>-1.5625</v>
@@ -10059,10 +10059,10 @@
         <v>0</v>
       </c>
       <c r="AA86">
-        <v>-4.6875</v>
+        <v>-3.125</v>
       </c>
       <c r="AB86" s="1">
-        <v>-5.5837900000000003E-5</v>
+        <v>-1.11676E-5</v>
       </c>
       <c r="AC86">
         <v>-3.125</v>
@@ -10175,10 +10175,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>-6.25</v>
+        <v>-4.6875</v>
       </c>
       <c r="AB87" s="1">
-        <v>-1.45179E-4</v>
+        <v>-5.5837900000000003E-5</v>
       </c>
       <c r="AC87">
         <v>-4.6875</v>
@@ -10291,10 +10291,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>-7.8125</v>
+        <v>-6.25</v>
       </c>
       <c r="AB88" s="1">
-        <v>-3.3502800000000002E-4</v>
+        <v>-1.45179E-4</v>
       </c>
       <c r="AC88">
         <v>-6.25</v>
@@ -10407,10 +10407,10 @@
         <v>-1.11676E-5</v>
       </c>
       <c r="AA89">
-        <v>-9.375</v>
+        <v>-7.8125</v>
       </c>
       <c r="AB89" s="1">
-        <v>-5.33086E-4</v>
+        <v>-3.3502800000000002E-4</v>
       </c>
       <c r="AC89">
         <v>-7.8125</v>
@@ -10523,10 +10523,10 @@
         <v>-3.35028E-5</v>
       </c>
       <c r="AA90">
-        <v>-10.9375</v>
-      </c>
-      <c r="AB90">
-        <v>-2.0400000000000001E-3</v>
+        <v>-9.375</v>
+      </c>
+      <c r="AB90" s="1">
+        <v>-5.33086E-4</v>
       </c>
       <c r="AC90">
         <v>-9.375</v>
@@ -10639,10 +10639,10 @@
         <v>-7.8173100000000005E-5</v>
       </c>
       <c r="AA91">
-        <v>-14.0625</v>
+        <v>-10.9375</v>
       </c>
       <c r="AB91">
-        <v>-1.8429999999999998E-2</v>
+        <v>-2.0400000000000001E-3</v>
       </c>
       <c r="AC91">
         <v>-10.9375</v>
@@ -10755,10 +10755,10 @@
         <v>-1.7868100000000001E-4</v>
       </c>
       <c r="AA92">
-        <v>-15.625</v>
+        <v>-12.5</v>
       </c>
       <c r="AB92">
-        <v>-2.0500000000000001E-2</v>
+        <v>-1.0880000000000001E-2</v>
       </c>
       <c r="AC92">
         <v>-12.5</v>
@@ -10871,10 +10871,10 @@
         <v>-4.24368E-4</v>
       </c>
       <c r="AA93">
-        <v>-17.1875</v>
+        <v>-14.0625</v>
       </c>
       <c r="AB93">
-        <v>-2.257E-2</v>
+        <v>-1.8429999999999998E-2</v>
       </c>
       <c r="AC93">
         <v>-14.0625</v>
@@ -10987,10 +10987,10 @@
         <v>-5.7099999999999998E-3</v>
       </c>
       <c r="AA94">
-        <v>-18.75</v>
+        <v>-15.625</v>
       </c>
       <c r="AB94">
-        <v>-2.461E-2</v>
+        <v>-2.0500000000000001E-2</v>
       </c>
       <c r="AC94">
         <v>-15.625</v>
@@ -11103,10 +11103,10 @@
         <v>-2.264E-2</v>
       </c>
       <c r="AA95">
-        <v>-20.3125</v>
+        <v>-17.1875</v>
       </c>
       <c r="AB95">
-        <v>-2.6669999999999999E-2</v>
+        <v>-2.257E-2</v>
       </c>
       <c r="AC95">
         <v>-17.1875</v>
@@ -11219,10 +11219,10 @@
         <v>-2.469E-2</v>
       </c>
       <c r="AA96">
-        <v>-21.875</v>
+        <v>-18.75</v>
       </c>
       <c r="AB96">
-        <v>-2.8709999999999999E-2</v>
+        <v>-2.461E-2</v>
       </c>
       <c r="AC96">
         <v>-18.75</v>
@@ -11335,10 +11335,10 @@
         <v>-2.6759999999999999E-2</v>
       </c>
       <c r="AA97">
-        <v>-23.4375</v>
+        <v>-20.3125</v>
       </c>
       <c r="AB97">
-        <v>-3.0769999999999999E-2</v>
+        <v>-2.6669999999999999E-2</v>
       </c>
       <c r="AC97">
         <v>-20.3125</v>
@@ -11451,10 +11451,10 @@
         <v>-2.8799999999999999E-2</v>
       </c>
       <c r="AA98">
-        <v>-25</v>
+        <v>-21.875</v>
       </c>
       <c r="AB98">
-        <v>-3.2809999999999999E-2</v>
+        <v>-2.8709999999999999E-2</v>
       </c>
       <c r="AC98">
         <v>-21.875</v>
@@ -11567,10 +11567,10 @@
         <v>-3.0870000000000002E-2</v>
       </c>
       <c r="AA99">
-        <v>-26.5625</v>
+        <v>-23.4375</v>
       </c>
       <c r="AB99">
-        <v>-3.4849999999999999E-2</v>
+        <v>-3.0769999999999999E-2</v>
       </c>
       <c r="AC99">
         <v>-23.4375</v>
@@ -11683,10 +11683,10 @@
         <v>-3.2919999999999998E-2</v>
       </c>
       <c r="AA100">
-        <v>-28.125</v>
+        <v>-25</v>
       </c>
       <c r="AB100">
-        <v>-3.6900000000000002E-2</v>
+        <v>-3.2809999999999999E-2</v>
       </c>
       <c r="AC100">
         <v>-25</v>
@@ -11799,10 +11799,10 @@
         <v>-3.4970000000000001E-2</v>
       </c>
       <c r="AA101">
-        <v>-29.6875</v>
+        <v>-26.5625</v>
       </c>
       <c r="AB101">
-        <v>-3.8960000000000002E-2</v>
+        <v>-3.4849999999999999E-2</v>
       </c>
       <c r="AC101">
         <v>-26.5625</v>
@@ -11915,10 +11915,10 @@
         <v>-3.7019999999999997E-2</v>
       </c>
       <c r="AA102">
-        <v>-31.25</v>
+        <v>-28.125</v>
       </c>
       <c r="AB102">
-        <v>-4.1009999999999998E-2</v>
+        <v>-3.6900000000000002E-2</v>
       </c>
       <c r="AC102">
         <v>-28.125</v>
@@ -12031,10 +12031,10 @@
         <v>-3.909E-2</v>
       </c>
       <c r="AA103">
-        <v>-32.8125</v>
+        <v>-29.6875</v>
       </c>
       <c r="AB103">
-        <v>-4.3049999999999998E-2</v>
+        <v>-3.8960000000000002E-2</v>
       </c>
       <c r="AC103">
         <v>-29.6875</v>
@@ -12147,10 +12147,10 @@
         <v>-4.1140000000000003E-2</v>
       </c>
       <c r="AA104">
-        <v>-34.375</v>
+        <v>-31.25</v>
       </c>
       <c r="AB104">
-        <v>-4.5089999999999998E-2</v>
+        <v>-4.1009999999999998E-2</v>
       </c>
       <c r="AC104">
         <v>-31.25</v>
@@ -12263,10 +12263,10 @@
         <v>-4.3189999999999999E-2</v>
       </c>
       <c r="AA105">
-        <v>-35.9375</v>
+        <v>-32.8125</v>
       </c>
       <c r="AB105">
-        <v>-4.7149999999999997E-2</v>
+        <v>-4.3049999999999998E-2</v>
       </c>
       <c r="AC105">
         <v>-32.8125</v>
@@ -12379,10 +12379,10 @@
         <v>-4.5240000000000002E-2</v>
       </c>
       <c r="AA106">
-        <v>-37.5</v>
+        <v>-34.375</v>
       </c>
       <c r="AB106">
-        <v>-4.9189999999999998E-2</v>
+        <v>-4.5089999999999998E-2</v>
       </c>
       <c r="AC106">
         <v>-34.375</v>
@@ -12495,10 +12495,10 @@
         <v>-4.7289999999999999E-2</v>
       </c>
       <c r="AA107">
-        <v>-39.0625</v>
+        <v>-35.9375</v>
       </c>
       <c r="AB107">
-        <v>-5.126E-2</v>
+        <v>-4.7149999999999997E-2</v>
       </c>
       <c r="AC107">
         <v>-35.9375</v>
@@ -12611,10 +12611,10 @@
         <v>-4.9349999999999998E-2</v>
       </c>
       <c r="AA108">
-        <v>-40.625</v>
+        <v>-37.5</v>
       </c>
       <c r="AB108">
-        <v>-5.33E-2</v>
+        <v>-4.9189999999999998E-2</v>
       </c>
       <c r="AC108">
         <v>-37.5</v>
@@ -12727,10 +12727,10 @@
         <v>-5.142E-2</v>
       </c>
       <c r="AA109">
-        <v>-42.1875</v>
+        <v>-39.0625</v>
       </c>
       <c r="AB109">
-        <v>-5.5359999999999999E-2</v>
+        <v>-5.126E-2</v>
       </c>
       <c r="AC109">
         <v>-39.0625</v>
@@ -12843,10 +12843,10 @@
         <v>-5.3469999999999997E-2</v>
       </c>
       <c r="AA110">
-        <v>-43.75</v>
+        <v>-40.625</v>
       </c>
       <c r="AB110">
-        <v>-5.74E-2</v>
+        <v>-5.33E-2</v>
       </c>
       <c r="AC110">
         <v>-40.625</v>
@@ -12959,10 +12959,10 @@
         <v>-5.5539999999999999E-2</v>
       </c>
       <c r="AA111">
-        <v>-45.3125</v>
+        <v>-42.1875</v>
       </c>
       <c r="AB111">
-        <v>-5.9459999999999999E-2</v>
+        <v>-5.5359999999999999E-2</v>
       </c>
       <c r="AC111">
         <v>-42.1875</v>
@@ -13075,10 +13075,10 @@
         <v>-5.7579999999999999E-2</v>
       </c>
       <c r="AA112">
-        <v>-46.875</v>
+        <v>-43.75</v>
       </c>
       <c r="AB112">
-        <v>-6.1499999999999999E-2</v>
+        <v>-5.74E-2</v>
       </c>
       <c r="AC112">
         <v>-43.75</v>
@@ -13191,10 +13191,10 @@
         <v>-5.9630000000000002E-2</v>
       </c>
       <c r="AA113">
-        <v>-48.4375</v>
+        <v>-45.3125</v>
       </c>
       <c r="AB113">
-        <v>-6.3549999999999995E-2</v>
+        <v>-5.9459999999999999E-2</v>
       </c>
       <c r="AC113">
         <v>-45.3125</v>
@@ -13307,10 +13307,10 @@
         <v>-6.1690000000000002E-2</v>
       </c>
       <c r="AA114">
-        <v>-50</v>
+        <v>-46.875</v>
       </c>
       <c r="AB114">
-        <v>-6.5600000000000006E-2</v>
+        <v>-6.1499999999999999E-2</v>
       </c>
       <c r="AC114">
         <v>-46.875</v>
@@ -13423,10 +13423,10 @@
         <v>-6.3759999999999997E-2</v>
       </c>
       <c r="AA115">
-        <v>-51.5625</v>
+        <v>-48.4375</v>
       </c>
       <c r="AB115">
-        <v>-6.7720000000000002E-2</v>
+        <v>-6.3549999999999995E-2</v>
       </c>
       <c r="AC115">
         <v>-48.4375</v>
@@ -13539,10 +13539,10 @@
         <v>-6.5809999999999994E-2</v>
       </c>
       <c r="AA116">
-        <v>-53.125</v>
+        <v>-50</v>
       </c>
       <c r="AB116">
-        <v>-6.9760000000000003E-2</v>
+        <v>-6.5600000000000006E-2</v>
       </c>
       <c r="AC116">
         <v>-50</v>
@@ -13655,10 +13655,10 @@
         <v>-6.7930000000000004E-2</v>
       </c>
       <c r="AA117">
-        <v>-54.6875</v>
+        <v>-51.5625</v>
       </c>
       <c r="AB117">
-        <v>-7.1830000000000005E-2</v>
+        <v>-6.7720000000000002E-2</v>
       </c>
       <c r="AC117">
         <v>-51.5625</v>
@@ -13771,10 +13771,10 @@
         <v>-6.9980000000000001E-2</v>
       </c>
       <c r="AA118">
-        <v>-56.25</v>
+        <v>-53.125</v>
       </c>
       <c r="AB118">
-        <v>-7.3870000000000005E-2</v>
+        <v>-6.9760000000000003E-2</v>
       </c>
       <c r="AC118">
         <v>-53.125</v>
@@ -13887,10 +13887,10 @@
         <v>-7.2040000000000007E-2</v>
       </c>
       <c r="AA119">
-        <v>-57.8125</v>
+        <v>-54.6875</v>
       </c>
       <c r="AB119">
-        <v>-7.5929999999999997E-2</v>
+        <v>-7.1830000000000005E-2</v>
       </c>
       <c r="AC119">
         <v>-54.6875</v>
@@ -14003,10 +14003,10 @@
         <v>-7.4099999999999999E-2</v>
       </c>
       <c r="AA120">
-        <v>-59.375</v>
+        <v>-56.25</v>
       </c>
       <c r="AB120">
-        <v>-7.7990000000000004E-2</v>
+        <v>-7.3870000000000005E-2</v>
       </c>
       <c r="AC120">
         <v>-56.25</v>
@@ -14119,10 +14119,10 @@
         <v>-7.6149999999999995E-2</v>
       </c>
       <c r="AA121">
-        <v>-60.9375</v>
+        <v>-57.8125</v>
       </c>
       <c r="AB121">
-        <v>-8.0049999999999996E-2</v>
+        <v>-7.5929999999999997E-2</v>
       </c>
       <c r="AC121">
         <v>-57.8125</v>
@@ -14235,10 +14235,10 @@
         <v>-7.8219999999999998E-2</v>
       </c>
       <c r="AA122">
-        <v>-60.9375</v>
+        <v>-59.375</v>
       </c>
       <c r="AB122">
-        <v>-7.986E-2</v>
+        <v>-7.7990000000000004E-2</v>
       </c>
       <c r="AC122">
         <v>-59.375</v>
@@ -14351,10 +14351,10 @@
         <v>-8.0280000000000004E-2</v>
       </c>
       <c r="AA123">
-        <v>-59.375</v>
+        <v>-60.9375</v>
       </c>
       <c r="AB123">
-        <v>-7.7789999999999998E-2</v>
+        <v>-8.0049999999999996E-2</v>
       </c>
       <c r="AC123">
         <v>-60.9375</v>
@@ -14467,10 +14467,10 @@
         <v>-8.0030000000000004E-2</v>
       </c>
       <c r="AA124">
-        <v>-57.8125</v>
+        <v>-60.9375</v>
       </c>
       <c r="AB124">
-        <v>-7.5749999999999998E-2</v>
+        <v>-7.986E-2</v>
       </c>
       <c r="AC124">
         <v>-60.9375</v>
@@ -14583,10 +14583,10 @@
         <v>-7.7960000000000002E-2</v>
       </c>
       <c r="AA125">
-        <v>-56.25</v>
+        <v>-59.375</v>
       </c>
       <c r="AB125">
-        <v>-7.3690000000000005E-2</v>
+        <v>-7.7789999999999998E-2</v>
       </c>
       <c r="AC125">
         <v>-59.375</v>
@@ -14699,10 +14699,10 @@
         <v>-7.5910000000000005E-2</v>
       </c>
       <c r="AA126">
-        <v>-54.6875</v>
+        <v>-57.8125</v>
       </c>
       <c r="AB126">
-        <v>-7.1639999999999995E-2</v>
+        <v>-7.5749999999999998E-2</v>
       </c>
       <c r="AC126">
         <v>-57.8125</v>
@@ -14815,10 +14815,10 @@
         <v>-7.3840000000000003E-2</v>
       </c>
       <c r="AA127">
-        <v>-53.125</v>
+        <v>-56.25</v>
       </c>
       <c r="AB127">
-        <v>-6.9570000000000007E-2</v>
+        <v>-7.3690000000000005E-2</v>
       </c>
       <c r="AC127">
         <v>-56.25</v>
@@ -14931,10 +14931,10 @@
         <v>-7.1800000000000003E-2</v>
       </c>
       <c r="AA128">
-        <v>-51.5625</v>
+        <v>-54.6875</v>
       </c>
       <c r="AB128">
-        <v>-6.7519999999999997E-2</v>
+        <v>-7.1639999999999995E-2</v>
       </c>
       <c r="AC128">
         <v>-54.6875</v>
@@ -15047,10 +15047,10 @@
         <v>-6.973E-2</v>
       </c>
       <c r="AA129">
-        <v>-50</v>
+        <v>-53.125</v>
       </c>
       <c r="AB129">
-        <v>-6.54E-2</v>
+        <v>-6.9570000000000007E-2</v>
       </c>
       <c r="AC129">
         <v>-53.125</v>
@@ -15163,10 +15163,10 @@
         <v>-6.7680000000000004E-2</v>
       </c>
       <c r="AA130">
-        <v>-48.4375</v>
+        <v>-51.5625</v>
       </c>
       <c r="AB130">
-        <v>-6.3339999999999994E-2</v>
+        <v>-6.7519999999999997E-2</v>
       </c>
       <c r="AC130">
         <v>-51.5625</v>
@@ -15279,10 +15279,10 @@
         <v>-6.5540000000000001E-2</v>
       </c>
       <c r="AA131">
-        <v>-46.875</v>
+        <v>-50</v>
       </c>
       <c r="AB131">
-        <v>-6.1280000000000001E-2</v>
+        <v>-6.54E-2</v>
       </c>
       <c r="AC131">
         <v>-50</v>
@@ -15395,10 +15395,10 @@
         <v>-6.3490000000000005E-2</v>
       </c>
       <c r="AA132">
-        <v>-45.3125</v>
+        <v>-48.4375</v>
       </c>
       <c r="AB132">
-        <v>-5.9229999999999998E-2</v>
+        <v>-6.3339999999999994E-2</v>
       </c>
       <c r="AC132">
         <v>-48.4375</v>
@@ -15511,10 +15511,10 @@
         <v>-6.1420000000000002E-2</v>
       </c>
       <c r="AA133">
-        <v>-43.75</v>
+        <v>-46.875</v>
       </c>
       <c r="AB133">
-        <v>-5.7180000000000002E-2</v>
+        <v>-6.1280000000000001E-2</v>
       </c>
       <c r="AC133">
         <v>-46.875</v>
@@ -15627,10 +15627,10 @@
         <v>-5.9369999999999999E-2</v>
       </c>
       <c r="AA134">
-        <v>-42.1875</v>
+        <v>-45.3125</v>
       </c>
       <c r="AB134">
-        <v>-5.5129999999999998E-2</v>
+        <v>-5.9229999999999998E-2</v>
       </c>
       <c r="AC134">
         <v>-45.3125</v>
@@ -15743,10 +15743,10 @@
         <v>-5.731E-2</v>
       </c>
       <c r="AA135">
-        <v>-40.625</v>
+        <v>-43.75</v>
       </c>
       <c r="AB135">
-        <v>-5.3080000000000002E-2</v>
+        <v>-5.7180000000000002E-2</v>
       </c>
       <c r="AC135">
         <v>-43.75</v>
@@ -15859,10 +15859,10 @@
         <v>-5.5259999999999997E-2</v>
       </c>
       <c r="AA136">
-        <v>-39.0625</v>
+        <v>-42.1875</v>
       </c>
       <c r="AB136">
-        <v>-5.1020000000000003E-2</v>
+        <v>-5.5129999999999998E-2</v>
       </c>
       <c r="AC136">
         <v>-42.1875</v>
@@ -15975,10 +15975,10 @@
         <v>-5.3190000000000001E-2</v>
       </c>
       <c r="AA137">
-        <v>-37.5</v>
+        <v>-40.625</v>
       </c>
       <c r="AB137">
-        <v>-4.8959999999999997E-2</v>
+        <v>-5.3080000000000002E-2</v>
       </c>
       <c r="AC137">
         <v>-40.625</v>
@@ -16091,10 +16091,10 @@
         <v>-5.1139999999999998E-2</v>
       </c>
       <c r="AA138">
-        <v>-35.9375</v>
+        <v>-39.0625</v>
       </c>
       <c r="AB138">
-        <v>-4.6920000000000003E-2</v>
+        <v>-5.1020000000000003E-2</v>
       </c>
       <c r="AC138">
         <v>-39.0625</v>
@@ -16207,10 +16207,10 @@
         <v>-4.9070000000000003E-2</v>
       </c>
       <c r="AA139">
-        <v>-34.375</v>
+        <v>-37.5</v>
       </c>
       <c r="AB139">
-        <v>-4.4859999999999997E-2</v>
+        <v>-4.8959999999999997E-2</v>
       </c>
       <c r="AC139">
         <v>-37.5</v>
@@ -16323,10 +16323,10 @@
         <v>-4.7019999999999999E-2</v>
       </c>
       <c r="AA140">
-        <v>-32.8125</v>
+        <v>-35.9375</v>
       </c>
       <c r="AB140">
-        <v>-4.2810000000000001E-2</v>
+        <v>-4.6920000000000003E-2</v>
       </c>
       <c r="AC140">
         <v>-35.9375</v>
@@ -16439,10 +16439,10 @@
         <v>-4.496E-2</v>
       </c>
       <c r="AA141">
-        <v>-31.25</v>
+        <v>-34.375</v>
       </c>
       <c r="AB141">
-        <v>-4.0759999999999998E-2</v>
+        <v>-4.4859999999999997E-2</v>
       </c>
       <c r="AC141">
         <v>-34.375</v>
@@ -16555,10 +16555,10 @@
         <v>-4.2909999999999997E-2</v>
       </c>
       <c r="AA142">
-        <v>-29.6875</v>
+        <v>-32.8125</v>
       </c>
       <c r="AB142">
-        <v>-3.8710000000000001E-2</v>
+        <v>-4.2810000000000001E-2</v>
       </c>
       <c r="AC142">
         <v>-32.8125</v>
@@ -16671,10 +16671,10 @@
         <v>-4.086E-2</v>
       </c>
       <c r="AA143">
-        <v>-28.125</v>
+        <v>-31.25</v>
       </c>
       <c r="AB143">
-        <v>-3.6650000000000002E-2</v>
+        <v>-4.0759999999999998E-2</v>
       </c>
       <c r="AC143">
         <v>-31.25</v>
@@ -16787,10 +16787,10 @@
         <v>-3.8809999999999997E-2</v>
       </c>
       <c r="AA144">
-        <v>-26.5625</v>
+        <v>-29.6875</v>
       </c>
       <c r="AB144">
-        <v>-3.4610000000000002E-2</v>
+        <v>-3.8710000000000001E-2</v>
       </c>
       <c r="AC144">
         <v>-29.6875</v>
@@ -16903,10 +16903,10 @@
         <v>-3.6740000000000002E-2</v>
       </c>
       <c r="AA145">
-        <v>-25</v>
+        <v>-28.125</v>
       </c>
       <c r="AB145">
-        <v>-3.2559999999999999E-2</v>
+        <v>-3.6650000000000002E-2</v>
       </c>
       <c r="AC145">
         <v>-28.125</v>
@@ -17019,10 +17019,10 @@
         <v>-3.4689999999999999E-2</v>
       </c>
       <c r="AA146">
-        <v>-23.4375</v>
+        <v>-26.5625</v>
       </c>
       <c r="AB146">
-        <v>-3.0519999999999999E-2</v>
+        <v>-3.4610000000000002E-2</v>
       </c>
       <c r="AC146">
         <v>-26.5625</v>
@@ -17135,10 +17135,10 @@
         <v>-3.2640000000000002E-2</v>
       </c>
       <c r="AA147">
-        <v>-21.875</v>
+        <v>-25</v>
       </c>
       <c r="AB147">
-        <v>-2.8469999999999999E-2</v>
+        <v>-3.2559999999999999E-2</v>
       </c>
       <c r="AC147">
         <v>-25</v>
@@ -17251,10 +17251,10 @@
         <v>-3.0589999999999999E-2</v>
       </c>
       <c r="AA148">
-        <v>-20.3125</v>
+        <v>-23.4375</v>
       </c>
       <c r="AB148">
-        <v>-2.6409999999999999E-2</v>
+        <v>-3.0519999999999999E-2</v>
       </c>
       <c r="AC148">
         <v>-23.4375</v>
@@ -17367,10 +17367,10 @@
         <v>-2.853E-2</v>
       </c>
       <c r="AA149">
-        <v>-18.75</v>
+        <v>-21.875</v>
       </c>
       <c r="AB149">
-        <v>-2.4369999999999999E-2</v>
+        <v>-2.8469999999999999E-2</v>
       </c>
       <c r="AC149">
         <v>-21.875</v>
@@ -17483,10 +17483,10 @@
         <v>-2.648E-2</v>
       </c>
       <c r="AA150">
-        <v>-17.1875</v>
+        <v>-20.3125</v>
       </c>
       <c r="AB150">
-        <v>-2.232E-2</v>
+        <v>-2.6409999999999999E-2</v>
       </c>
       <c r="AC150">
         <v>-20.3125</v>
@@ -17599,10 +17599,10 @@
         <v>-2.4420000000000001E-2</v>
       </c>
       <c r="AA151">
-        <v>-15.625</v>
+        <v>-18.75</v>
       </c>
       <c r="AB151">
-        <v>-2.027E-2</v>
+        <v>-2.4369999999999999E-2</v>
       </c>
       <c r="AC151">
         <v>-18.75</v>
@@ -17715,10 +17715,10 @@
         <v>-2.2380000000000001E-2</v>
       </c>
       <c r="AA152">
-        <v>-14.0625</v>
+        <v>-17.1875</v>
       </c>
       <c r="AB152">
-        <v>-1.821E-2</v>
+        <v>-2.232E-2</v>
       </c>
       <c r="AC152">
         <v>-17.1875</v>
@@ -17831,10 +17831,10 @@
         <v>-2.0310000000000002E-2</v>
       </c>
       <c r="AA153">
-        <v>-12.5</v>
+        <v>-15.625</v>
       </c>
       <c r="AB153">
-        <v>-1.6109999999999999E-2</v>
+        <v>-2.027E-2</v>
       </c>
       <c r="AC153">
         <v>-15.625</v>
@@ -17947,10 +17947,10 @@
         <v>-1.8239999999999999E-2</v>
       </c>
       <c r="AA154">
-        <v>-10.9375</v>
+        <v>-14.0625</v>
       </c>
       <c r="AB154">
-        <v>-1.357E-2</v>
+        <v>-1.821E-2</v>
       </c>
       <c r="AC154">
         <v>-14.0625</v>
@@ -18063,10 +18063,10 @@
         <v>-1.5679999999999999E-2</v>
       </c>
       <c r="AA155">
-        <v>-9.375</v>
+        <v>-12.5</v>
       </c>
       <c r="AB155">
-        <v>-8.5500000000000003E-3</v>
+        <v>-1.6109999999999999E-2</v>
       </c>
       <c r="AC155">
         <v>-12.5</v>
@@ -18179,10 +18179,10 @@
         <v>-9.3200000000000002E-3</v>
       </c>
       <c r="AA156">
-        <v>-7.8125</v>
+        <v>-10.9375</v>
       </c>
       <c r="AB156">
-        <v>-2.5600000000000002E-3</v>
+        <v>-1.357E-2</v>
       </c>
       <c r="AC156">
         <v>-10.9375</v>
@@ -18295,10 +18295,10 @@
         <v>-1.2800000000000001E-3</v>
       </c>
       <c r="AA157">
-        <v>-6.25</v>
+        <v>-9.375</v>
       </c>
       <c r="AB157" s="1">
-        <v>-7.2589300000000002E-4</v>
+        <v>-8.5500000000000003E-3</v>
       </c>
       <c r="AC157">
         <v>-9.375</v>
@@ -18411,10 +18411,10 @@
         <v>-2.3451900000000001E-4</v>
       </c>
       <c r="AA158">
-        <v>-4.6875</v>
+        <v>-7.8125</v>
       </c>
       <c r="AB158" s="1">
-        <v>-2.3451900000000001E-4</v>
+        <v>-2.5600000000000002E-3</v>
       </c>
       <c r="AC158">
         <v>-7.8125</v>
@@ -18527,10 +18527,10 @@
         <v>-5.5837900000000003E-5</v>
       </c>
       <c r="AA159">
-        <v>-3.125</v>
+        <v>-6.25</v>
       </c>
       <c r="AB159" s="1">
-        <v>-4.4670299999999998E-5</v>
+        <v>-7.2589300000000002E-4</v>
       </c>
       <c r="AC159">
         <v>-6.25</v>
@@ -18643,10 +18643,10 @@
         <v>-1.11676E-5</v>
       </c>
       <c r="AA160">
-        <v>-1.5625</v>
-      </c>
-      <c r="AB160">
-        <v>0</v>
+        <v>-4.6875</v>
+      </c>
+      <c r="AB160" s="1">
+        <v>-2.3451900000000001E-4</v>
       </c>
       <c r="AC160">
         <v>-4.6875</v>
@@ -18758,6 +18758,12 @@
       <c r="Z161">
         <v>0</v>
       </c>
+      <c r="AA161">
+        <v>-3.125</v>
+      </c>
+      <c r="AB161" s="1">
+        <v>-4.4670299999999998E-5</v>
+      </c>
       <c r="AC161">
         <v>-3.125</v>
       </c>
@@ -18866,6 +18872,12 @@
         <v>-1.5625</v>
       </c>
       <c r="Z162">
+        <v>0</v>
+      </c>
+      <c r="AA162">
+        <v>-1.5625</v>
+      </c>
+      <c r="AB162">
         <v>0</v>
       </c>
       <c r="AC162">
